--- a/utils/monday_sprint_sprint_2023-16.xlsx
+++ b/utils/monday_sprint_sprint_2023-16.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="168">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>21490</t>
+    <t>4890408785</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>28/07/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>13/08/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>4892576292</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -111,7 +111,10 @@
     <t>Produtivo em horas</t>
   </si>
   <si>
-    <t>21088</t>
+    <t>12/08/2023</t>
+  </si>
+  <si>
+    <t>4900120491</t>
   </si>
   <si>
     <t>Sistema de controle de peças a serem destruídas</t>
@@ -123,7 +126,7 @@
     <t>Semana 5</t>
   </si>
   <si>
-    <t>8474</t>
+    <t>4952133698</t>
   </si>
   <si>
     <t>Alteração da planilha do MPS para apresentar as colunas: Tempo Prod. Médio e Tempo CPP</t>
@@ -141,10 +144,13 @@
     <t>Agosto</t>
   </si>
   <si>
+    <t>4952150909</t>
+  </si>
+  <si>
     <t>Verificar possibilidade de apresentar tempos de usinagem em consulta no sistema ( Mostrar dados no fluxo e FTF )</t>
   </si>
   <si>
-    <t>21101</t>
+    <t>4811898560</t>
   </si>
   <si>
     <t>Relatório das informações "F9" do SPS - Análise</t>
@@ -153,13 +159,13 @@
     <t>14/07/2023</t>
   </si>
   <si>
-    <t>21470</t>
+    <t>4890422148</t>
   </si>
   <si>
     <t>Visualização - Sistema desmoldagem</t>
   </si>
   <si>
-    <t>21382</t>
+    <t>4890584576</t>
   </si>
   <si>
     <t>Alteração na tela causas</t>
@@ -168,43 +174,46 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>21379</t>
+    <t>4890604564</t>
   </si>
   <si>
     <t>Seq Ativas sem Pedidos</t>
   </si>
   <si>
-    <t>21298</t>
+    <t>4890672844</t>
   </si>
   <si>
     <t>Relatório do sistema de desmoldagem</t>
   </si>
   <si>
-    <t>21228</t>
+    <t>07/08/2023</t>
+  </si>
+  <si>
+    <t>4890756310</t>
   </si>
   <si>
     <t>Alteração sistema de apontamento - Apontamento Pintura</t>
   </si>
   <si>
-    <t>21227</t>
+    <t>4890764763</t>
   </si>
   <si>
     <t>Alteração sistema de apontamento - Apontamento Inspeção</t>
   </si>
   <si>
-    <t>21226</t>
+    <t>4890776971</t>
   </si>
   <si>
     <t>Alteração sistema de apontamento - Apontamento Eletronico Acabamento</t>
   </si>
   <si>
-    <t>21223</t>
+    <t>4891615501</t>
   </si>
   <si>
     <t>Alteração sistema de apontamento - Apontamento Ajustagem</t>
   </si>
   <si>
-    <t>21006</t>
+    <t>4735669412</t>
   </si>
   <si>
     <t>Sequência "poluídas" no MPS</t>
@@ -216,85 +225,97 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>21467</t>
+    <t>4890450653</t>
   </si>
   <si>
     <t>Acesso Debit Memo</t>
   </si>
   <si>
-    <t>21230</t>
+    <t>4890701280</t>
   </si>
   <si>
     <t>Relatório Carteira Orçamentos Ativos</t>
   </si>
   <si>
-    <t>21229</t>
+    <t>4890717082</t>
   </si>
   <si>
     <t>Alteração sistema de apontamento - Apontamento Tratamento Térmico</t>
   </si>
   <si>
-    <t>21225</t>
+    <t>06/08/2023</t>
+  </si>
+  <si>
+    <t>4891600084</t>
   </si>
   <si>
     <t>Alteração sistema de apontamento - Apontamento Solda</t>
   </si>
   <si>
-    <t>21009</t>
+    <t>4891666458</t>
   </si>
   <si>
     <t>Habilitar a opção de eliminar Invoice de pagamento dentro da Proforma</t>
   </si>
   <si>
-    <t>20339</t>
+    <t>01/08/2023</t>
+  </si>
+  <si>
+    <t>4891728089</t>
   </si>
   <si>
     <t>Verificar Campo de Observação das Invoices de Pagamento - Feito na Sprint 14</t>
   </si>
   <si>
-    <t>20876</t>
+    <t>4893267182</t>
   </si>
   <si>
     <t>Informação de Sequencia na CPC</t>
   </si>
   <si>
-    <t>18631</t>
+    <t>4901414042</t>
   </si>
   <si>
     <t>Novo relatório - Relatório de Custos por Nota Fiscal</t>
   </si>
   <si>
-    <t>21446</t>
+    <t>4890509099</t>
   </si>
   <si>
     <t>Melhoria no relatório de Entrada por ordem de compra</t>
   </si>
   <si>
-    <t>21426</t>
+    <t>4890524009</t>
   </si>
   <si>
     <t>Botão envio volume mensageria SEFAZ no sistema de serviços</t>
   </si>
   <si>
-    <t>21340</t>
+    <t>30/07/2023</t>
+  </si>
+  <si>
+    <t>4890641791</t>
   </si>
   <si>
     <t>Melhoria para sistema de modelos</t>
   </si>
   <si>
-    <t>21066/21231</t>
+    <t>4890691248</t>
   </si>
   <si>
     <t>Alteração Relatório Cálculo Custeio - Sistema de Corridas</t>
   </si>
   <si>
-    <t>21213</t>
+    <t>4891628030</t>
   </si>
   <si>
     <t>Upload Arquivo p/geração ordem de compra</t>
   </si>
   <si>
-    <t>21330</t>
+    <t>03/08/2023</t>
+  </si>
+  <si>
+    <t>4900943304</t>
   </si>
   <si>
     <t>Indefinido</t>
@@ -306,21 +327,30 @@
     <t>Não definida</t>
   </si>
   <si>
-    <t>21224</t>
+    <t>4903079525</t>
   </si>
   <si>
     <t>Melhorias continuas lançamento NFs</t>
   </si>
   <si>
-    <t>21138</t>
+    <t>4891643673</t>
   </si>
   <si>
     <t>Alteração Relatório PCP - Saída Corte de Canais</t>
   </si>
   <si>
+    <t>10/08/2023</t>
+  </si>
+  <si>
+    <t>4952188996</t>
+  </si>
+  <si>
     <t>Carga histórica dos tempos de usinagem</t>
   </si>
   <si>
+    <t>4952194661</t>
+  </si>
+  <si>
     <t>Rotina de cálculo mensal e atualização dos tempos de usinagem</t>
   </si>
   <si>
@@ -330,6 +360,9 @@
     <t>Atividades Diversas</t>
   </si>
   <si>
+    <t>4838132642</t>
+  </si>
+  <si>
     <t>Tempos de Usinagem (tempos no roteiro)</t>
   </si>
   <si>
@@ -339,33 +372,42 @@
     <t>Semana 3</t>
   </si>
   <si>
+    <t>4892437204</t>
+  </si>
+  <si>
     <t>4903918022</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>4924703124</t>
   </si>
   <si>
     <t>Teste com pré embarque</t>
   </si>
   <si>
-    <t>03/08/2023</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
+    <t>4924708348</t>
+  </si>
+  <si>
     <t>Acompanhar os testes com o inventário</t>
   </si>
   <si>
-    <t>21513</t>
+    <t>4925498146</t>
   </si>
   <si>
     <t>Consulta Ordens de Movimentação</t>
   </si>
   <si>
+    <t>4925557719</t>
+  </si>
+  <si>
     <t>Consulta Estoque Por Área por Modelo</t>
   </si>
   <si>
+    <t>4925577741</t>
+  </si>
+  <si>
     <t>Consulta Contentor</t>
   </si>
   <si>
@@ -381,7 +423,7 @@
     <t>Importação de dados com calculo de valores errados</t>
   </si>
   <si>
-    <t>19084</t>
+    <t>4927429874</t>
   </si>
   <si>
     <t>Alteração de alçada de aprovação</t>
@@ -393,7 +435,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-16</t>
+    <t>Jun/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -1035,7 +1077,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1052,7 +1094,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1064,10 +1106,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1079,10 +1121,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1091,7 +1133,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1099,7 +1141,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1111,13 +1153,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1126,10 +1168,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1138,15 +1180,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1158,42 +1200,42 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1205,10 +1247,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1220,7 +1262,7 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>24</v>
@@ -1232,7 +1274,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1240,7 +1282,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1252,10 +1294,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1270,7 +1312,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1287,7 +1329,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1299,13 +1341,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1317,7 +1359,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1334,7 +1376,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1346,10 +1388,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1364,7 +1406,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1381,7 +1423,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1393,10 +1435,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1411,7 +1453,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1428,7 +1470,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1440,10 +1482,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1458,7 +1500,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1475,7 +1517,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1487,10 +1529,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1505,7 +1547,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1522,7 +1564,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1534,10 +1576,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1552,7 +1594,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1569,7 +1611,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1581,10 +1623,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1599,7 +1641,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1616,7 +1658,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1628,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1643,10 +1685,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1655,15 +1697,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1675,10 +1717,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1693,7 +1735,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1710,7 +1752,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1722,10 +1764,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1740,7 +1782,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1757,7 +1799,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1769,10 +1811,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1787,7 +1829,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1804,7 +1846,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1816,10 +1858,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1834,7 +1876,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1851,7 +1893,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1863,10 +1905,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1881,7 +1923,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1898,7 +1940,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1910,10 +1952,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1928,7 +1970,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1945,7 +1987,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1957,10 +1999,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1975,7 +2017,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1992,7 +2034,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2004,10 +2046,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2019,10 +2061,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2031,7 +2073,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2039,7 +2081,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2051,10 +2093,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2069,7 +2111,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2086,7 +2128,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2098,10 +2140,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2116,7 +2158,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2133,7 +2175,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2145,10 +2187,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2163,7 +2205,7 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2180,7 +2222,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2192,10 +2234,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2210,7 +2252,7 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2227,7 +2269,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2239,10 +2281,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2257,7 +2299,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2274,25 +2316,25 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2301,10 +2343,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2313,7 +2355,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2321,7 +2363,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2333,10 +2375,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2348,10 +2390,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2360,7 +2402,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2368,7 +2410,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2380,10 +2422,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2398,7 +2440,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2415,7 +2457,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2427,13 +2469,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2442,10 +2484,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2454,15 +2496,15 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2474,13 +2516,13 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2489,10 +2531,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2501,34 +2543,34 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
       </c>
@@ -2536,7 +2578,7 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -2548,7 +2590,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2556,7 +2598,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2568,13 +2610,13 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>21</v>
@@ -2583,10 +2625,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2595,7 +2637,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2603,7 +2645,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2615,13 +2657,13 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>21</v>
@@ -2633,7 +2675,7 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2650,25 +2692,25 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -2677,7 +2719,7 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>24</v>
@@ -2689,7 +2731,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2697,7 +2739,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2709,13 +2751,13 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>21</v>
@@ -2724,10 +2766,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2736,15 +2778,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2756,13 +2798,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>21</v>
@@ -2771,10 +2813,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2783,15 +2825,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2803,10 +2845,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2818,10 +2860,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2830,15 +2872,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2850,10 +2892,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2865,10 +2907,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2877,15 +2919,15 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2897,10 +2939,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2912,10 +2954,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2924,33 +2966,33 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -2959,7 +3001,7 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>24</v>
@@ -2971,7 +3013,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -2979,25 +3021,25 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -3006,10 +3048,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3018,7 +3060,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3026,7 +3068,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3038,37 +3080,37 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="O46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3084,23 +3126,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3108,16 +3150,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3128,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3136,7 +3178,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3149,7 +3191,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3157,7 +3199,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3188,12 +3230,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>45</v>
@@ -3207,7 +3249,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3217,25 +3259,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3252,13 +3294,13 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3270,10 +3312,10 @@
         <v>45</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3284,7 +3326,7 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -3296,21 +3338,21 @@
         <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -3322,73 +3364,61 @@
         <v>30</v>
       </c>
       <c r="J12" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="Q12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="M14" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q14">
-        <v>9</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3396,7 +3426,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3404,7 +3434,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3412,10 +3442,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3423,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3437,7 +3467,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -3445,128 +3475,128 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
